--- a/data/gravel/Falkenjagd Aristos SL 2025.xlsx
+++ b/data/gravel/Falkenjagd Aristos SL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED60AC57-F99A-FD4A-A66F-F3FFBDCAC5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD14A83-ECF7-2347-9B39-C0C43CE7B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="960" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>fake</t>
+  </si>
+  <si>
+    <t>https://shop.1bike4life.com/thumbnail/28/35/ea/1751289817/Falkenjagd_Aristos_SL_Juni_2025_Studio_White-3303_1920x1920.jpg?ts=1751289823</t>
   </si>
 </sst>
 </file>
@@ -760,6 +763,11 @@
         <v>82</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Falkenjagd Aristos SL 2025.xlsx
+++ b/data/gravel/Falkenjagd Aristos SL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD14A83-ECF7-2347-9B39-C0C43CE7B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC45A1F-CF74-E34E-8A96-93770B638F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="960" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -284,9 +284,6 @@
     <t>https://shop.1bike4life.com/Falkenjagd-ARISTOS-SL-Gravel-Rahmenset-2025/SW10103</t>
   </si>
   <si>
-    <t>euros</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -345,6 +342,15 @@
   </si>
   <si>
     <t>https://shop.1bike4life.com/thumbnail/28/35/ea/1751289817/Falkenjagd_Aristos_SL_Juni_2025_Studio_White-3303_1920x1920.jpg?ts=1751289823</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Garching, Bavaria, Germany</t>
   </si>
 </sst>
 </file>
@@ -717,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -765,7 +771,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -773,7 +779,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -784,22 +790,22 @@
         <v>77</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H8" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -807,7 +813,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="6">
         <v>470</v>
@@ -830,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="6">
         <v>530</v>
@@ -853,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="6">
         <v>130</v>
@@ -876,7 +882,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="6">
         <v>71</v>
@@ -899,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="6">
         <v>74</v>
@@ -922,7 +928,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="6">
         <v>425</v>
@@ -945,7 +951,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="6">
         <v>72</v>
@@ -968,7 +974,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" s="6">
         <v>1005</v>
@@ -991,7 +997,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="6">
         <v>378</v>
@@ -1014,7 +1020,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" s="6">
         <v>555</v>
@@ -1057,7 +1063,7 @@
         <v>44</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1372,7 +1378,7 @@
         <v>52</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1466,7 +1472,15 @@
         <v>66</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>83</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Falkenjagd Aristos SL 2025.xlsx
+++ b/data/gravel/Falkenjagd Aristos SL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC45A1F-CF74-E34E-8A96-93770B638F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8988B167-6453-F84B-8700-DFFB59AB00EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="960" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>Garching, Bavaria, Germany</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -723,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1321,165 +1339,195 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B70">
-        <v>4990</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="1"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>104</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>105</v>
       </c>
     </row>
